--- a/Result/profitability/3085.xlsx
+++ b/Result/profitability/3085.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.24125</v>
+        <v>-0.1825</v>
       </c>
       <c r="N2" t="n">
-        <v>52.3125</v>
+        <v>57.10625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.31</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.13125</v>
+        <v>-0.0525</v>
       </c>
       <c r="N3" t="n">
-        <v>57.515</v>
+        <v>61.68</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03875</v>
+        <v>-0.03</v>
       </c>
       <c r="N4" t="n">
-        <v>62.35375</v>
+        <v>63.80249999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.05624999999999999</v>
+        <v>-0.0525</v>
       </c>
       <c r="N5" t="n">
-        <v>63.43625</v>
+        <v>64.0175</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0275</v>
+        <v>-0.01999999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>64.49250000000001</v>
+        <v>66.57875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.09</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00375</v>
+        <v>0.003750000000000003</v>
       </c>
       <c r="N7" t="n">
-        <v>66.8425</v>
+        <v>65.32875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.15</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.002499999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="N8" t="n">
-        <v>65.35124999999999</v>
+        <v>64.435</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1899,10 +1899,10 @@
         <v>0.21</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.065</v>
+        <v>-0.06499999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>61.53500000000001</v>
+        <v>61.535</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>-0.22</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.05375000000000001</v>
+        <v>-0.05374999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>62.065</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3085</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>23</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14</v>
+      </c>
+      <c r="F75" t="n">
+        <v>61.77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-55.03%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>51.125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5833333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-7.329999999999991</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1060781476121562</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2307692307692307</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.650000000000006</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.08140756302521024</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
